--- a/human_validation/judge/kor/judge_D019_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S005_P003__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 먼저, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 손자가 죽은 이후로 저는... 그냥 더 이상 따뜻함이 느껴지지가 않아요. 딸이 제 옆에 앉아서 손을 잡아줘도, 제가 딸을 사랑한다는 건 아는데, 마땅히 느껴져야 할 것처럼 속으로는 느껴지지가 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 속으로 따뜻함이 느껴지지 않는다고 하셨는데, 그것과 더불어 자신의 몸에서 동떨어져 있거나 마치 밖에서 자신을 지켜보는 것 같은 느낌도 드시나요, 아니면 주로 감정 자체가 무뎌진 느낌인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 주로 감정이에요. 몸 밖에 있는 것 같은 느낌은 안 들어요. 그냥... 딸이 제 손을 잡아줘도, 딸을 사랑한다는 건 아는데, 그 따뜻함이 더 이상 속에서 느껴지지가 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 배제됨: 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 손자분이 돌아가신 이후로, 원치 않는데도 그분이 돌아가신 상황에 대한 기억이나 악몽, 플래시백이 마음속에 불쑥 떠오르는 일이 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 퀼트 조각을 접거나 차를 집으려고 손을 뻗다가도, 갑자기 그 총소리가 다시 들리고 커뮤니티 센터 밖에 누워 있는 손자의 모습이 보여요. 마치 바로 제 눈앞에서 일어나는 일처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 배제됨: 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 손자분이 돌아가신 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 이제 6일 됐어요, 커뮤니티 센터 밖에서 손자가 죽은 지 6일이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 배제됨: 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 총격 사건 이후로, 평소와 다르게 예민하거나 긴장되거나, 잠들기 어렵거나, 집중하기 힘든 느낌을 받으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 제빙기에서 얼음 몇 개 떨어지는 소리에도 온몸이 움찔해요. 식탁을 붙잡게 되고, 다른 사람들은 다 진정된 후에도 한참 동안 심장이 쿵쾅거려요. 동네에서 차가 역화하는 소리도 똑같이 그래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 배제됨: 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 급성 스트레스장애 (D019)
 인구통계: 성별 여성 / 나이 84 / 직업상태 not in workforce / 최종학력 대학 재학
@@ -575,173 +684,36 @@
 증상 지속 기간: 6 days
 추가 요건: 
 주호소 증상 코드: S076
-배경 서술: 글로리아의 성인 손자는 그녀의 퀼트 전시와 세대 통합 청소년 프로그램에 필요한 물품을 자주 날라주던 사람이었는데, 계획 회의에 참석하라고 그녀를 내려준 직후 커뮤니티 센터 밖에서 벌어진 갑작스러운 총격 사건으로 목숨을 잃었다. 그녀는 총소리를 들었고, 응급 구조대원들이 그녀를 자리에서 데려가기 전에 그 참혹한 현장을 목격했으며, 이 상실은 그녀의 가족과 지역사회 생활의 중심을 강타했다. 이후 6일 동안 그녀는 커뮤니티 센터와 세컨드라인 음악, 심지어 사건이 일어난 거리까지도 피했고, 원치 않는 기억이 하루 중 불쑥 끼어들었으며, 익숙한 방들이 낯설게 느껴졌고, 찾아오는 친척들에게 따뜻함을 느낄 수 없었으며, 평범한 집안 소음에도 날카로운 분노나 과도한 놀람으로 반응했다. 그녀가 걷기 모임에 나가지 않게 되고 장례식 뒤풀이 준비를 도울 수 없을 만큼 힘들어하자, 딸과 목사가 그녀를 정신과 응급 진료소로 데려갔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 먼저, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 손자가 죽은 이후로 저는... 그냥 더 이상 따뜻함이 느껴지지가 않아요. 딸이 제 옆에 앉아서 손을 잡아줘도, 제가 딸을 사랑한다는 건 아는데, 마땅히 느껴져야 할 것처럼 속으로는 느껴지지가 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 속으로 따뜻함이 느껴지지 않는다고 하셨는데, 그것과 더불어 자신의 몸에서 동떨어져 있거나 마치 밖에서 자신을 지켜보는 것 같은 느낌도 드시나요, 아니면 주로 감정 자체가 무뎌진 느낌인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 주로 감정이에요. 몸 밖에 있는 것 같은 느낌은 안 들어요. 그냥... 딸이 제 손을 잡아줘도, 딸을 사랑한다는 건 아는데, 그 따뜻함이 더 이상 속에서 느껴지지가 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 배제됨: 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 손자분이 돌아가신 이후로, 원치 않는데도 그분이 돌아가신 상황에 대한 기억이나 악몽, 플래시백이 마음속에 불쑥 떠오르는 일이 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 퀼트 조각을 접거나 차를 집으려고 손을 뻗다가도, 갑자기 그 총소리가 다시 들리고 커뮤니티 센터 밖에 누워 있는 손자의 모습이 보여요. 마치 바로 제 눈앞에서 일어나는 일처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 배제됨: 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 손자분이 돌아가신 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 이제 6일 됐어요, 커뮤니티 센터 밖에서 손자가 죽은 지 6일이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 배제됨: 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 총격 사건 이후로, 평소와 다르게 예민하거나 긴장되거나, 잠들기 어렵거나, 집중하기 힘든 느낌을 받으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 제빙기에서 얼음 몇 개 떨어지는 소리에도 온몸이 움찔해요. 식탁을 붙잡게 되고, 다른 사람들은 다 진정된 후에도 한참 동안 심장이 쿵쾅거려요. 동네에서 차가 역화하는 소리도 똑같이 그래요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: 글로리아의 성인 손자는 그녀의 퀼트 전시와 세대 통합 청소년 프로그램에 필요한 물품을 자주 날라주던 사람이었는데, 계획 회의에 참석하라고 그녀를 내려준 직후 커뮤니티 센터 밖에서 벌어진 갑작스러운 총격 사건으로 목숨을 잃었다. 그녀는 총소리를 들었고, 응급 구조대원들이 그녀를 자리에서 데려가기 전에 그 참혹한 현장을 목격했으며, 이 상실은 그녀의 가족과 지역사회 생활의 중심을 강타했다. 이후 6일 동안 그녀는 커뮤니티 센터와 세컨드라인 음악, 심지어 사건이 일어난 거리까지도 피했고, 원치 않는 기억이 하루 중 불쑥 끼어들었으며, 익숙한 방들이 낯설게 느껴졌고, 찾아오는 친척들에게 따뜻함을 느낄 수 없었으며, 평범한 집안 소음에도 날카로운 분노나 과도한 놀람으로 반응했다. 그녀가 걷기 모임에 나가지 않게 되고 장례식 뒤풀이 준비를 도울 수 없을 만큼 힘들어하자, 딸과 목사가 그녀를 정신과 응급 진료소로 데려갔다.
+표집된 증상 목록:
+  - S069 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - S070 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+  - S076 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - S077 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.
+  - S080 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.
+  - S082 이인증/비현실감: 외상 사건 이후 자기 자신이나 주변 환경에 대한 현실감이 변화된 상태.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 배제됨: 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 급성 스트레스장애 (D019, ICD: F43.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: acute_stress_symptoms (관계=must_include, 요구개수=6, 충족개수=3, 커버리지=0.5)
-  확인된 근거: 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.; 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).; 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.; 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).; 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.; 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.; 이인증/비현실감: 외상 사건 이후 자기 자신이나 주변 환경에 대한 현실감이 변화된 상태.</t>
+          <t>의사의 최종 진단: 급성 스트레스장애 (D019, ICD: F43.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: acute_stress_symptoms (관계=must_include, 요구개수=6, 충족개수=3, 커버리지=0.5)
+확인된 근거:
+  - 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D019_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S005_P003__claude-sonnet-5_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -709,11 +714,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D019_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S005_P003__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
